--- a/request_forms/010_custom_pc_build_request--request_forms.xlsx
+++ b/request_forms/010_custom_pc_build_request--request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>gaming_pc</t>
+          <t>gaming pc</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>socket_amd</t>
+          <t>socket amd</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>socket_amd_thread_mrp</t>
+          <t>socket amd thread mrp</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>socket_intel</t>
+          <t>socket intel</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>socket_intel_l</t>
+          <t>socket intel l</t>
         </is>
       </c>
     </row>
@@ -1253,7 +1253,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>sdd_nvm</t>
+          <t>sdd nvm</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>atx_nps</t>
+          <t>atx nps</t>
         </is>
       </c>
     </row>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>atx_npw</t>
+          <t>atx npw</t>
         </is>
       </c>
     </row>
